--- a/outputs/Redditch Library - Fenster Pricing Document.xlsx
+++ b/outputs/Redditch Library - Fenster Pricing Document.xlsx
@@ -1598,7 +1598,7 @@
       </c>
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n">
-        <v>51.85</v>
+        <v>51.62</v>
       </c>
       <c r="M9" s="4">
         <f>IF(B9="CW",SUM(O9*850),0)</f>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n">
-        <v>51.85</v>
+        <v>51.62</v>
       </c>
       <c r="M10" s="4">
         <f>IF(B10="CW",SUM(O10*850),0)</f>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n">
-        <v>59.13</v>
+        <v>58.86</v>
       </c>
       <c r="M11" s="4">
         <f>IF(B11="CW",SUM(O11*850),0)</f>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n">
-        <v>59.13</v>
+        <v>58.86</v>
       </c>
       <c r="M12" s="4">
         <f>IF(B12="CW",SUM(O12*850),0)</f>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n">
-        <v>59.13</v>
+        <v>58.86</v>
       </c>
       <c r="M13" s="4">
         <f>IF(B13="CW",SUM(O13*850),0)</f>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n">
-        <v>59.13</v>
+        <v>58.86</v>
       </c>
       <c r="M14" s="4">
         <f>IF(B14="CW",SUM(O14*850),0)</f>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n">
-        <v>59.13</v>
+        <v>58.86</v>
       </c>
       <c r="M15" s="4">
         <f>IF(B15="CW",SUM(O15*850),0)</f>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n">
-        <v>59.13</v>
+        <v>58.86</v>
       </c>
       <c r="M16" s="4">
         <f>IF(B16="CW",SUM(O16*850),0)</f>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n">
-        <v>51.83</v>
+        <v>51.6</v>
       </c>
       <c r="M17" s="4">
         <f>IF(B17="CW",SUM(O17*850),0)</f>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n">
-        <v>51.83</v>
+        <v>51.6</v>
       </c>
       <c r="M18" s="4">
         <f>IF(B18="CW",SUM(O18*850),0)</f>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n">
-        <v>51.83</v>
+        <v>51.6</v>
       </c>
       <c r="M19" s="4">
         <f>IF(B19="CW",SUM(O19*850),0)</f>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n">
-        <v>51.83</v>
+        <v>51.6</v>
       </c>
       <c r="M20" s="4">
         <f>IF(B20="CW",SUM(O20*850),0)</f>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="K21" s="4" t="n"/>
       <c r="L21" s="4" t="n">
-        <v>51.83</v>
+        <v>51.6</v>
       </c>
       <c r="M21" s="4">
         <f>IF(B21="CW",SUM(O21*850),0)</f>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K22" s="4" t="n"/>
       <c r="L22" s="4" t="n">
-        <v>51.83</v>
+        <v>51.6</v>
       </c>
       <c r="M22" s="4">
         <f>IF(B22="CW",SUM(O22*850),0)</f>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="K23" s="4" t="n"/>
       <c r="L23" s="4" t="n">
-        <v>32.92</v>
+        <v>32.77</v>
       </c>
       <c r="M23" s="4">
         <f>IF(B23="CW",SUM(O23*850),0)</f>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n">
-        <v>61.52</v>
+        <v>61.25</v>
       </c>
       <c r="M24" s="4">
         <f>IF(B24="CW",SUM(O24*850),0)</f>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="4" t="n">
-        <v>61.52</v>
+        <v>61.25</v>
       </c>
       <c r="M25" s="4">
         <f>IF(B25="CW",SUM(O25*850),0)</f>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="K26" s="4" t="n"/>
       <c r="L26" s="4" t="n">
-        <v>61.52</v>
+        <v>61.25</v>
       </c>
       <c r="M26" s="4">
         <f>IF(B26="CW",SUM(O26*850),0)</f>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n">
-        <v>112.53</v>
+        <v>548.9299999999999</v>
       </c>
       <c r="M27" s="4">
         <f>IF(B27="CW",SUM(O27*850),0)</f>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n">
-        <v>76.77</v>
+        <v>410.53</v>
       </c>
       <c r="M28" s="4">
         <f>IF(B28="CW",SUM(O28*850),0)</f>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K29" s="4" t="n"/>
       <c r="L29" s="4" t="n">
-        <v>32.92</v>
+        <v>32.77</v>
       </c>
       <c r="M29" s="4">
         <f>IF(B29="CW",SUM(O29*850),0)</f>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n">
-        <v>33.49</v>
+        <v>33.34</v>
       </c>
       <c r="M30" s="4">
         <f>IF(B30="CW",SUM(O30*850),0)</f>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n">
-        <v>33.49</v>
+        <v>33.34</v>
       </c>
       <c r="M31" s="4">
         <f>IF(B31="CW",SUM(O31*850),0)</f>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n">
-        <v>21.62</v>
+        <v>21.52</v>
       </c>
       <c r="M32" s="4">
         <f>IF(B32="CW",SUM(O32*850),0)</f>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n">
-        <v>21.62</v>
+        <v>21.52</v>
       </c>
       <c r="M33" s="4">
         <f>IF(B33="CW",SUM(O33*850),0)</f>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K34" s="4" t="n"/>
       <c r="L34" s="4" t="n">
-        <v>21.62</v>
+        <v>21.52</v>
       </c>
       <c r="M34" s="4">
         <f>IF(B34="CW",SUM(O34*850),0)</f>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n">
-        <v>21.62</v>
+        <v>21.52</v>
       </c>
       <c r="M35" s="4">
         <f>IF(B35="CW",SUM(O35*850),0)</f>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="K36" s="4" t="n"/>
       <c r="L36" s="4" t="n">
-        <v>21.62</v>
+        <v>21.52</v>
       </c>
       <c r="M36" s="4">
         <f>IF(B36="CW",SUM(O36*850),0)</f>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n">
-        <v>18.21</v>
+        <v>18.13</v>
       </c>
       <c r="M37" s="4">
         <f>IF(B37="CW",SUM(O37*850),0)</f>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="K38" s="4" t="n"/>
       <c r="L38" s="4" t="n">
-        <v>18.21</v>
+        <v>18.13</v>
       </c>
       <c r="M38" s="4">
         <f>IF(B38="CW",SUM(O38*850),0)</f>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="K39" s="4" t="n"/>
       <c r="L39" s="4" t="n">
-        <v>18.21</v>
+        <v>18.13</v>
       </c>
       <c r="M39" s="4">
         <f>IF(B39="CW",SUM(O39*850),0)</f>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n">
-        <v>46.88</v>
+        <v>46.67</v>
       </c>
       <c r="M40" s="4">
         <f>IF(B40="CW",SUM(O40*850),0)</f>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="K41" s="4" t="n"/>
       <c r="L41" s="4" t="n">
-        <v>57.43</v>
+        <v>57.17</v>
       </c>
       <c r="M41" s="4">
         <f>IF(B41="CW",SUM(O41*850),0)</f>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n">
-        <v>39.26</v>
+        <v>39.08</v>
       </c>
       <c r="M42" s="4">
         <f>IF(B42="CW",SUM(O42*850),0)</f>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="K43" s="4" t="n"/>
       <c r="L43" s="4" t="n">
-        <v>53.41</v>
+        <v>53.17</v>
       </c>
       <c r="M43" s="4">
         <f>IF(B43="CW",SUM(O43*850),0)</f>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n">
-        <v>52.82</v>
+        <v>52.58</v>
       </c>
       <c r="M44" s="4">
         <f>IF(B44="CW",SUM(O44*850),0)</f>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n">
-        <v>39.26</v>
+        <v>39.08</v>
       </c>
       <c r="M45" s="4">
         <f>IF(B45="CW",SUM(O45*850),0)</f>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n">
-        <v>39.26</v>
+        <v>39.08</v>
       </c>
       <c r="M46" s="4">
         <f>IF(B46="CW",SUM(O46*850),0)</f>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="K47" s="4" t="n"/>
       <c r="L47" s="4" t="n">
-        <v>57.91</v>
+        <v>57.65</v>
       </c>
       <c r="M47" s="4">
         <f>IF(B47="CW",SUM(O47*850),0)</f>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n">
-        <v>58.06</v>
+        <v>57.8</v>
       </c>
       <c r="M48" s="4">
         <f>IF(B48="CW",SUM(O48*850),0)</f>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="n">
-        <v>57.91</v>
+        <v>57.65</v>
       </c>
       <c r="M49" s="4">
         <f>IF(B49="CW",SUM(O49*850),0)</f>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n">
-        <v>30.53</v>
+        <v>30.39</v>
       </c>
       <c r="M50" s="4">
         <f>IF(B50="CW",SUM(O50*850),0)</f>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n">
-        <v>79.38</v>
+        <v>79.02</v>
       </c>
       <c r="M51" s="4">
         <f>IF(B51="CW",SUM(O51*850),0)</f>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="H52" s="101" t="n">
-        <v>1615.64</v>
+        <v>1615.44</v>
       </c>
       <c r="I52" s="102">
         <f>SUM(H52*F52)</f>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="H53" s="101" t="n">
-        <v>1865.53</v>
+        <v>1865.31</v>
       </c>
       <c r="I53" s="102">
         <f>SUM(H53*F53)</f>
@@ -4698,7 +4698,7 @@
       <c r="D54" s="90" t="n"/>
       <c r="E54" s="99" t="inlineStr">
         <is>
-          <t>43 openings</t>
+          <t>43 nr @ GBP 150.00</t>
         </is>
       </c>
       <c r="F54" s="91" t="n">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="H54" s="86" t="n">
-        <v>3084.28</v>
+        <v>6630.61</v>
       </c>
       <c r="I54" s="88">
         <f>SUM(H54*F54)</f>

--- a/outputs/Redditch Library - Fenster Pricing Document.xlsx
+++ b/outputs/Redditch Library - Fenster Pricing Document.xlsx
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E6" s="10" t="n"/>

--- a/outputs/Redditch Library - Fenster Pricing Document.xlsx
+++ b/outputs/Redditch Library - Fenster Pricing Document.xlsx
@@ -1594,11 +1594,11 @@
         <v/>
       </c>
       <c r="J9" s="93" t="n">
-        <v>1431.28</v>
+        <v>1468.11</v>
       </c>
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n">
-        <v>51.62</v>
+        <v>52.58</v>
       </c>
       <c r="M9" s="4">
         <f>IF(B9="CW",SUM(O9*850),0)</f>
@@ -1668,11 +1668,11 @@
         <v/>
       </c>
       <c r="J10" s="93" t="n">
-        <v>1431.28</v>
+        <v>1468.11</v>
       </c>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n">
-        <v>51.62</v>
+        <v>52.58</v>
       </c>
       <c r="M10" s="4">
         <f>IF(B10="CW",SUM(O10*850),0)</f>
@@ -1742,11 +1742,11 @@
         <v/>
       </c>
       <c r="J11" s="93" t="n">
-        <v>1690.1</v>
+        <v>1733.59</v>
       </c>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n">
-        <v>58.86</v>
+        <v>60</v>
       </c>
       <c r="M11" s="4">
         <f>IF(B11="CW",SUM(O11*850),0)</f>
@@ -1816,11 +1816,11 @@
         <v/>
       </c>
       <c r="J12" s="93" t="n">
-        <v>1690.1</v>
+        <v>1733.59</v>
       </c>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n">
-        <v>58.86</v>
+        <v>60</v>
       </c>
       <c r="M12" s="4">
         <f>IF(B12="CW",SUM(O12*850),0)</f>
@@ -1890,11 +1890,11 @@
         <v/>
       </c>
       <c r="J13" s="93" t="n">
-        <v>1690.1</v>
+        <v>1733.59</v>
       </c>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n">
-        <v>58.86</v>
+        <v>60</v>
       </c>
       <c r="M13" s="4">
         <f>IF(B13="CW",SUM(O13*850),0)</f>
@@ -1964,11 +1964,11 @@
         <v/>
       </c>
       <c r="J14" s="93" t="n">
-        <v>1690.1</v>
+        <v>1733.59</v>
       </c>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n">
-        <v>58.86</v>
+        <v>60</v>
       </c>
       <c r="M14" s="4">
         <f>IF(B14="CW",SUM(O14*850),0)</f>
@@ -2038,11 +2038,11 @@
         <v/>
       </c>
       <c r="J15" s="93" t="n">
-        <v>1690.1</v>
+        <v>1733.59</v>
       </c>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n">
-        <v>58.86</v>
+        <v>60</v>
       </c>
       <c r="M15" s="4">
         <f>IF(B15="CW",SUM(O15*850),0)</f>
@@ -2112,11 +2112,11 @@
         <v/>
       </c>
       <c r="J16" s="93" t="n">
-        <v>1690.1</v>
+        <v>1733.59</v>
       </c>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n">
-        <v>58.86</v>
+        <v>60</v>
       </c>
       <c r="M16" s="4">
         <f>IF(B16="CW",SUM(O16*850),0)</f>
@@ -2186,11 +2186,11 @@
         <v/>
       </c>
       <c r="J17" s="93" t="n">
-        <v>1430.52</v>
+        <v>1467.34</v>
       </c>
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n">
-        <v>51.6</v>
+        <v>52.56</v>
       </c>
       <c r="M17" s="4">
         <f>IF(B17="CW",SUM(O17*850),0)</f>
@@ -2260,11 +2260,11 @@
         <v/>
       </c>
       <c r="J18" s="93" t="n">
-        <v>1430.52</v>
+        <v>1467.34</v>
       </c>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n">
-        <v>51.6</v>
+        <v>52.56</v>
       </c>
       <c r="M18" s="4">
         <f>IF(B18="CW",SUM(O18*850),0)</f>
@@ -2334,11 +2334,11 @@
         <v/>
       </c>
       <c r="J19" s="93" t="n">
-        <v>1430.52</v>
+        <v>1467.34</v>
       </c>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n">
-        <v>51.6</v>
+        <v>52.56</v>
       </c>
       <c r="M19" s="4">
         <f>IF(B19="CW",SUM(O19*850),0)</f>
@@ -2408,11 +2408,11 @@
         <v/>
       </c>
       <c r="J20" s="103" t="n">
-        <v>1430.52</v>
+        <v>1467.34</v>
       </c>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n">
-        <v>51.6</v>
+        <v>52.56</v>
       </c>
       <c r="M20" s="4">
         <f>IF(B20="CW",SUM(O20*850),0)</f>
@@ -2478,11 +2478,11 @@
         <v/>
       </c>
       <c r="J21" s="103" t="n">
-        <v>1430.52</v>
+        <v>1467.34</v>
       </c>
       <c r="K21" s="4" t="n"/>
       <c r="L21" s="4" t="n">
-        <v>51.6</v>
+        <v>52.56</v>
       </c>
       <c r="M21" s="4">
         <f>IF(B21="CW",SUM(O21*850),0)</f>
@@ -2548,11 +2548,11 @@
         <v/>
       </c>
       <c r="J22" s="103" t="n">
-        <v>1430.52</v>
+        <v>1467.34</v>
       </c>
       <c r="K22" s="4" t="n"/>
       <c r="L22" s="4" t="n">
-        <v>51.6</v>
+        <v>52.56</v>
       </c>
       <c r="M22" s="4">
         <f>IF(B22="CW",SUM(O22*850),0)</f>
@@ -2618,11 +2618,11 @@
         <v/>
       </c>
       <c r="J23" s="103" t="n">
-        <v>833.0599999999999</v>
+        <v>854.5</v>
       </c>
       <c r="K23" s="4" t="n"/>
       <c r="L23" s="4" t="n">
-        <v>32.77</v>
+        <v>33.33</v>
       </c>
       <c r="M23" s="4">
         <f>IF(B23="CW",SUM(O23*850),0)</f>
@@ -2688,11 +2688,11 @@
         <v/>
       </c>
       <c r="J24" s="103" t="n">
-        <v>1775.26</v>
+        <v>1820.94</v>
       </c>
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n">
-        <v>61.25</v>
+        <v>62.44</v>
       </c>
       <c r="M24" s="4">
         <f>IF(B24="CW",SUM(O24*850),0)</f>
@@ -2758,11 +2758,11 @@
         <v/>
       </c>
       <c r="J25" s="103" t="n">
-        <v>1775.26</v>
+        <v>1820.94</v>
       </c>
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="4" t="n">
-        <v>61.25</v>
+        <v>62.44</v>
       </c>
       <c r="M25" s="4">
         <f>IF(B25="CW",SUM(O25*850),0)</f>
@@ -2828,11 +2828,11 @@
         <v/>
       </c>
       <c r="J26" s="103" t="n">
-        <v>1775.26</v>
+        <v>1820.94</v>
       </c>
       <c r="K26" s="4" t="n"/>
       <c r="L26" s="4" t="n">
-        <v>61.25</v>
+        <v>62.44</v>
       </c>
       <c r="M26" s="4">
         <f>IF(B26="CW",SUM(O26*850),0)</f>
@@ -2898,11 +2898,11 @@
         <v/>
       </c>
       <c r="J27" s="103" t="n">
-        <v>3364.24</v>
+        <v>3450.82</v>
       </c>
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n">
-        <v>548.9299999999999</v>
+        <v>551.1799999999999</v>
       </c>
       <c r="M27" s="4">
         <f>IF(B27="CW",SUM(O27*850),0)</f>
@@ -2968,11 +2968,11 @@
         <v/>
       </c>
       <c r="J28" s="103" t="n">
-        <v>2242.6</v>
+        <v>2300.32</v>
       </c>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n">
-        <v>410.53</v>
+        <v>412.03</v>
       </c>
       <c r="M28" s="4">
         <f>IF(B28="CW",SUM(O28*850),0)</f>
@@ -3038,11 +3038,11 @@
         <v/>
       </c>
       <c r="J29" s="103" t="n">
-        <v>833.0599999999999</v>
+        <v>854.5</v>
       </c>
       <c r="K29" s="4" t="n"/>
       <c r="L29" s="4" t="n">
-        <v>32.77</v>
+        <v>33.33</v>
       </c>
       <c r="M29" s="4">
         <f>IF(B29="CW",SUM(O29*850),0)</f>
@@ -3108,11 +3108,11 @@
         <v/>
       </c>
       <c r="J30" s="103" t="n">
-        <v>853.39</v>
+        <v>875.35</v>
       </c>
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n">
-        <v>33.34</v>
+        <v>33.91</v>
       </c>
       <c r="M30" s="4">
         <f>IF(B30="CW",SUM(O30*850),0)</f>
@@ -3178,11 +3178,11 @@
         <v/>
       </c>
       <c r="J31" s="103" t="n">
-        <v>853.39</v>
+        <v>875.35</v>
       </c>
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n">
-        <v>33.34</v>
+        <v>33.91</v>
       </c>
       <c r="M31" s="4">
         <f>IF(B31="CW",SUM(O31*850),0)</f>
@@ -3248,11 +3248,11 @@
         <v/>
       </c>
       <c r="J32" s="103" t="n">
-        <v>431.34</v>
+        <v>442.44</v>
       </c>
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n">
-        <v>21.52</v>
+        <v>21.81</v>
       </c>
       <c r="M32" s="4">
         <f>IF(B32="CW",SUM(O32*850),0)</f>
@@ -3318,11 +3318,11 @@
         <v/>
       </c>
       <c r="J33" s="103" t="n">
-        <v>431.34</v>
+        <v>442.44</v>
       </c>
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n">
-        <v>21.52</v>
+        <v>21.81</v>
       </c>
       <c r="M33" s="4">
         <f>IF(B33="CW",SUM(O33*850),0)</f>
@@ -3388,11 +3388,11 @@
         <v/>
       </c>
       <c r="J34" s="103" t="n">
-        <v>431.34</v>
+        <v>442.44</v>
       </c>
       <c r="K34" s="4" t="n"/>
       <c r="L34" s="4" t="n">
-        <v>21.52</v>
+        <v>21.81</v>
       </c>
       <c r="M34" s="4">
         <f>IF(B34="CW",SUM(O34*850),0)</f>
@@ -3458,11 +3458,11 @@
         <v/>
       </c>
       <c r="J35" s="103" t="n">
-        <v>431.34</v>
+        <v>442.44</v>
       </c>
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n">
-        <v>21.52</v>
+        <v>21.81</v>
       </c>
       <c r="M35" s="4">
         <f>IF(B35="CW",SUM(O35*850),0)</f>
@@ -3528,11 +3528,11 @@
         <v/>
       </c>
       <c r="J36" s="103" t="n">
-        <v>431.34</v>
+        <v>442.44</v>
       </c>
       <c r="K36" s="4" t="n"/>
       <c r="L36" s="4" t="n">
-        <v>21.52</v>
+        <v>21.81</v>
       </c>
       <c r="M36" s="4">
         <f>IF(B36="CW",SUM(O36*850),0)</f>
@@ -3598,11 +3598,11 @@
         <v/>
       </c>
       <c r="J37" s="103" t="n">
-        <v>309.93</v>
+        <v>317.91</v>
       </c>
       <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n">
-        <v>18.13</v>
+        <v>18.32</v>
       </c>
       <c r="M37" s="4">
         <f>IF(B37="CW",SUM(O37*850),0)</f>
@@ -3668,11 +3668,11 @@
         <v/>
       </c>
       <c r="J38" s="103" t="n">
-        <v>309.93</v>
+        <v>317.91</v>
       </c>
       <c r="K38" s="4" t="n"/>
       <c r="L38" s="4" t="n">
-        <v>18.13</v>
+        <v>18.32</v>
       </c>
       <c r="M38" s="4">
         <f>IF(B38="CW",SUM(O38*850),0)</f>
@@ -3738,11 +3738,11 @@
         <v/>
       </c>
       <c r="J39" s="103" t="n">
-        <v>309.93</v>
+        <v>317.91</v>
       </c>
       <c r="K39" s="4" t="n"/>
       <c r="L39" s="4" t="n">
-        <v>18.13</v>
+        <v>18.32</v>
       </c>
       <c r="M39" s="4">
         <f>IF(B39="CW",SUM(O39*850),0)</f>
@@ -3808,11 +3808,11 @@
         <v/>
       </c>
       <c r="J40" s="103" t="n">
-        <v>1254.53</v>
+        <v>1286.82</v>
       </c>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n">
-        <v>46.67</v>
+        <v>47.51</v>
       </c>
       <c r="M40" s="4">
         <f>IF(B40="CW",SUM(O40*850),0)</f>
@@ -3878,11 +3878,11 @@
         <v/>
       </c>
       <c r="J41" s="103" t="n">
-        <v>1142.18</v>
+        <v>1171.57</v>
       </c>
       <c r="K41" s="4" t="n"/>
       <c r="L41" s="4" t="n">
-        <v>57.17</v>
+        <v>57.92</v>
       </c>
       <c r="M41" s="4">
         <f>IF(B41="CW",SUM(O41*850),0)</f>
@@ -3948,11 +3948,11 @@
         <v/>
       </c>
       <c r="J42" s="103" t="n">
-        <v>1058.49</v>
+        <v>1085.73</v>
       </c>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n">
-        <v>39.08</v>
+        <v>39.79</v>
       </c>
       <c r="M42" s="4">
         <f>IF(B42="CW",SUM(O42*850),0)</f>
@@ -4018,11 +4018,11 @@
         <v/>
       </c>
       <c r="J43" s="103" t="n">
-        <v>1486.89</v>
+        <v>1525.15</v>
       </c>
       <c r="K43" s="4" t="n"/>
       <c r="L43" s="4" t="n">
-        <v>53.17</v>
+        <v>54.17</v>
       </c>
       <c r="M43" s="4">
         <f>IF(B43="CW",SUM(O43*850),0)</f>
@@ -4088,11 +4088,11 @@
         <v/>
       </c>
       <c r="J44" s="103" t="n">
-        <v>978.21</v>
+        <v>1003.39</v>
       </c>
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n">
-        <v>52.58</v>
+        <v>53.21</v>
       </c>
       <c r="M44" s="4">
         <f>IF(B44="CW",SUM(O44*850),0)</f>
@@ -4158,11 +4158,11 @@
         <v/>
       </c>
       <c r="J45" s="103" t="n">
-        <v>1058.49</v>
+        <v>1085.73</v>
       </c>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n">
-        <v>39.08</v>
+        <v>39.79</v>
       </c>
       <c r="M45" s="4">
         <f>IF(B45="CW",SUM(O45*850),0)</f>
@@ -4228,11 +4228,11 @@
         <v/>
       </c>
       <c r="J46" s="103" t="n">
-        <v>1058.49</v>
+        <v>1085.73</v>
       </c>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n">
-        <v>39.08</v>
+        <v>39.79</v>
       </c>
       <c r="M46" s="4">
         <f>IF(B46="CW",SUM(O46*850),0)</f>
@@ -4298,11 +4298,11 @@
         <v/>
       </c>
       <c r="J47" s="103" t="n">
-        <v>1159.39</v>
+        <v>1189.22</v>
       </c>
       <c r="K47" s="4" t="n"/>
       <c r="L47" s="4" t="n">
-        <v>57.65</v>
+        <v>58.41</v>
       </c>
       <c r="M47" s="4">
         <f>IF(B47="CW",SUM(O47*850),0)</f>
@@ -4368,11 +4368,11 @@
         <v/>
       </c>
       <c r="J48" s="103" t="n">
-        <v>1652.13</v>
+        <v>1694.65</v>
       </c>
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n">
-        <v>57.8</v>
+        <v>58.91</v>
       </c>
       <c r="M48" s="4">
         <f>IF(B48="CW",SUM(O48*850),0)</f>
@@ -4438,11 +4438,11 @@
         <v/>
       </c>
       <c r="J49" s="103" t="n">
-        <v>1159.39</v>
+        <v>1189.22</v>
       </c>
       <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="n">
-        <v>57.65</v>
+        <v>58.41</v>
       </c>
       <c r="M49" s="4">
         <f>IF(B49="CW",SUM(O49*850),0)</f>
@@ -4508,11 +4508,11 @@
         <v/>
       </c>
       <c r="J50" s="103" t="n">
-        <v>748.01</v>
+        <v>767.26</v>
       </c>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n">
-        <v>30.39</v>
+        <v>30.89</v>
       </c>
       <c r="M50" s="4">
         <f>IF(B50="CW",SUM(O50*850),0)</f>
@@ -4578,11 +4578,11 @@
         <v/>
       </c>
       <c r="J51" s="103" t="n">
-        <v>1322.73</v>
+        <v>1356.77</v>
       </c>
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n">
-        <v>79.02</v>
+        <v>79.87</v>
       </c>
       <c r="M51" s="4">
         <f>IF(B51="CW",SUM(O51*850),0)</f>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="H52" s="101" t="n">
-        <v>1615.44</v>
+        <v>1615.38</v>
       </c>
       <c r="I52" s="102">
         <f>SUM(H52*F52)</f>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="H53" s="101" t="n">
-        <v>1865.31</v>
+        <v>1865.24</v>
       </c>
       <c r="I53" s="102">
         <f>SUM(H53*F53)</f>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="H54" s="86" t="n">
-        <v>6630.61</v>
+        <v>6630.3</v>
       </c>
       <c r="I54" s="88">
         <f>SUM(H54*F54)</f>
